--- a/static/standards-correlations/Wyoming_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Wyoming_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$15</definedName>
@@ -550,10 +550,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | Effective July 2024, full district implementation 2026-27 - the 2020 set is superseded</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | Effective July 2024, full district implementation 2026-27 - the 2020 set is superseded</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -587,7 +588,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -644,7 +645,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Ext 1.2D (Abstraction Levels) is this standard almost exactly - it separates application software, system software, and hardware as levels and asks students to place their own program among them. Ext 3.1E (Computer vs. Peripheral) distinguishes the processor running the compiled program from the memory holding it and from motors and sensors as peripherals. Both are optional Extensions. In core, PreLab 1 boots the controller and runs a typed program and Unit 3.3 exposes source and header files in the IDE's Advanced mode, but the three-layer INTERACTION Wyoming asks students to explain is not developed. Discovery Systems 8 asks where meaning is lost between software, translator, and hardware.</t>
+          <t>Ext 1.2D (Abstraction Levels) is this standard almost exactly - it separates application software, system software, and hardware as levels and asks students to place their own program among them. Ext 3.1E (Computer vs. Peripheral) distinguishes the processor running the compiled program from the memory holding it and from motors and sensors as peripherals. Both are optional Extensions. In core, PreLab 1 boots the controller and runs a typed program and Unit 3.3 exposes source and header files in the IDE's Advanced mode, but the three-layer INTERACTION Wyoming asks students to explain is not developed. Introductory Systems 8 asks where meaning is lost between software, translator, and hardware.</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1009,7 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>The collaborative-tools half is met in core and met well: Unit 5.3 has students create a GitHub account and repository, add a README and an open-source license, and explain push and pull - the actual collaborative tool of the industry, not a proxy for it. Lab 5.3 core teaches the MIT License by name: what it permits and the single condition it imposes. Teams build and run every mission together, and Discovery Systems 3 makes the cost of uncoordinated work explicit. WHAT IS MISSING IS TEAM ROLES: no lab assigns, rotates, or assesses defined roles within the team. That same gap appears in Virginia CSF.AP.8, Texas 1(F), and Wisconsin PRO.4, so it is a curriculum-level absence rather than a Wyoming-specific one.</t>
+          <t>The collaborative-tools half is met in core and met well: Unit 5.3 has students create a GitHub account and repository, add a README and an open-source license, and explain push and pull - the actual collaborative tool of the industry, not a proxy for it. Lab 5.3 core teaches the MIT License by name: what it permits and the single condition it imposes. Teams build and run every mission together, and Introductory Systems 3 makes the cost of uncoordinated work explicit. WHAT IS MISSING IS TEAM ROLES: no lab assigns, rotates, or assesses defined roles within the team. That same gap appears in Virginia CSF.AP.8, Texas 1(F), and Wisconsin PRO.4, so it is a curriculum-level absence rather than a Wyoming-specific one.</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1103,7 @@
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>All three impact types have core evidence. LEGAL: Lab 5.3 core teaches the MIT License by name: what it permits and the single condition it imposes. and Unit 5.3 asks what could go wrong publishing a file with no license. SOCIAL and ETHICAL: Nineteen reflection prompts address responsibility for automated-system errors (navigation misroute, spam misflag, freight misclassification). and Discovery Systems 12 asks whose responsibility it is to anticipate harm from something genuinely useful - which is the positive-intent-with-harmful-outcome case Wyoming's framing implies. Ext 5.2D (Should It Exist?) requires a credible-source judgment on whether a real deployed system should exist. NOTE: MALICIOUS INTENT is the thinner half - Ext 5.3E (Ethical Use and the Rules) asks whether copying unlicensed code is ethical and what the school Acceptable Use Policy permits, but deliberate misuse, attack, and malware are not addressed anywhere.</t>
+          <t>All three impact types have core evidence. LEGAL: Lab 5.3 core teaches the MIT License by name: what it permits and the single condition it imposes. and Unit 5.3 asks what could go wrong publishing a file with no license. SOCIAL and ETHICAL: Nineteen reflection prompts address responsibility for automated-system errors (navigation misroute, spam misflag, freight misclassification). and Introductory Systems 12 asks whose responsibility it is to anticipate harm from something genuinely useful - which is the positive-intent-with-harmful-outcome case Wyoming's framing implies. Ext 5.2D (Should It Exist?) requires a credible-source judgment on whether a real deployed system should exist. NOTE: MALICIOUS INTENT is the thinner half - Ext 5.3E (Ethical Use and the Rules) asks whether copying unlicensed code is ethical and what the school Acceptable Use Policy permits, but deliberate misuse, attack, and malware are not addressed anywhere.</t>
         </is>
       </c>
     </row>
@@ -1136,6 +1137,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -1180,7 +1182,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1194,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -1328,6 +1330,8 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
@@ -1367,7 +1371,7 @@
 WDE contact: Sara Schnell, Supervisor of Standards, 307-777-5506, sara.schnell@wyo.gov
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow AND satisfaction of Wyoming's Proficient student descriptor. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the Proficient descriptor is only partly met.
 RESULT: 6 Full, 5 Partial, 0 BLANK of 11. Every Wyoming high school standard is addressed somewhere.
   Algorithms &amp; Programming  5 Full, 1 Partial of 6  - and this is 55% of the band
